--- a/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>LASE</t>
   </si>
@@ -1743,26 +1743,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1777,7 +1777,7 @@
         <v>1500</v>
       </c>
       <c r="E48" s="3">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="F48" s="3">
         <v>1000</v>
@@ -1807,7 +1807,7 @@
         <v>2900</v>
       </c>
       <c r="E49" s="3">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="F49" s="3">
         <v>3200</v>
@@ -2165,7 +2165,7 @@
         <v>500</v>
       </c>
       <c r="E62" s="3">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="F62" s="3">
         <v>1200</v>
@@ -3066,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>LASE</t>
   </si>
@@ -656,43 +656,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -705,24 +705,27 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>5000</v>
+        <v>3900</v>
       </c>
       <c r="E8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F8" s="3">
         <v>4200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2200</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -735,24 +738,27 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="E9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F9" s="3">
         <v>1500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>900</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,24 +771,27 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="E10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F10" s="3">
         <v>2600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1200</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -795,9 +804,12 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,16 +822,17 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,9 +885,12 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -899,23 +918,26 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
+        <v>400</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -929,9 +951,12 @@
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,23 +966,24 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5900</v>
+        <v>7700</v>
       </c>
       <c r="E17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
       </c>
@@ -970,23 +996,26 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1000</v>
+        <v>-3800</v>
       </c>
       <c r="E18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F18" s="3">
         <v>600</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
+      <c r="G18" s="3">
+        <v>0</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1000,9 +1029,12 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,8 +1047,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1029,8 +1062,8 @@
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1044,23 +1077,26 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-600</v>
+        <v>-3200</v>
       </c>
       <c r="E21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F21" s="3">
         <v>1000</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+      <c r="G21" s="3">
+        <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1074,9 +1110,12 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1089,8 +1128,8 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1104,23 +1143,26 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1000</v>
+        <v>-3800</v>
       </c>
       <c r="E23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
+      <c r="G23" s="3">
+        <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1134,9 +1176,12 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1149,8 +1194,8 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1164,9 +1209,12 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,23 +1242,26 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1000</v>
+        <v>-3800</v>
       </c>
       <c r="E26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
+      <c r="G26" s="3">
+        <v>0</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1224,23 +1275,26 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1000</v>
+        <v>-3800</v>
       </c>
       <c r="E27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
+      <c r="G27" s="3">
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1254,9 +1308,12 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,9 +1440,12 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1389,8 +1458,8 @@
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1404,23 +1473,26 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1000</v>
+        <v>-3800</v>
       </c>
       <c r="E33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
+      <c r="G33" s="3">
+        <v>0</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1434,9 +1506,12 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,23 +1539,26 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1000</v>
+        <v>-3800</v>
       </c>
       <c r="E35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
+      <c r="G35" s="3">
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1494,29 +1572,32 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1529,9 +1610,12 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,23 +1643,24 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E41" s="3">
         <v>12200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1587,9 +1673,12 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1617,24 +1706,27 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1647,24 +1739,27 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1700</v>
+        <v>2300</v>
       </c>
       <c r="E44" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F44" s="3">
         <v>1800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2200</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1677,17 +1772,20 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
         <v>0</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="E45" s="3">
+        <v>100</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1704,27 +1802,30 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>15200</v>
+        <v>9300</v>
       </c>
       <c r="E46" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F46" s="3">
         <v>2500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3300</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,39 +1838,45 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>300</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1777,14 +1884,14 @@
         <v>1500</v>
       </c>
       <c r="E48" s="3">
-        <v>2500</v>
+        <v>3400</v>
       </c>
       <c r="F48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G48" s="3">
         <v>1000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1797,23 +1904,26 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2900</v>
+        <v>4300</v>
       </c>
       <c r="E49" s="3">
-        <v>3600</v>
+        <v>5900</v>
       </c>
       <c r="F49" s="3">
         <v>3200</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
+      <c r="G49" s="3">
+        <v>3200</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1827,9 +1937,12 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,23 +2003,26 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+      <c r="G52" s="3">
+        <v>0</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1917,9 +2036,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,24 +2069,27 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>19700</v>
+        <v>15200</v>
       </c>
       <c r="E54" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F54" s="3">
         <v>6900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7500</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1977,9 +2102,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,16 +2135,17 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
+      <c r="E57" s="3">
+        <v>200</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2032,12 +2162,15 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2065,24 +2198,27 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="E59" s="3">
+        <v>800</v>
+      </c>
+      <c r="F59" s="3">
         <v>400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,24 +2231,27 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="E60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F60" s="3">
         <v>400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2125,9 +2264,12 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2155,24 +2297,27 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
         <v>500</v>
       </c>
-      <c r="E62" s="3">
-        <v>1800</v>
-      </c>
       <c r="F62" s="3">
+        <v>900</v>
+      </c>
+      <c r="G62" s="3">
         <v>1200</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,9 +2330,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,24 +2429,27 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="E66" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F66" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2305,9 +2462,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,23 +2609,26 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-700</v>
+        <v>-5700</v>
       </c>
       <c r="E72" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F72" s="3">
         <v>300</v>
       </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+      <c r="G72" s="3">
+        <v>0</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2469,9 +2642,12 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,24 +2741,27 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>17500</v>
+        <v>13500</v>
       </c>
       <c r="E76" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F76" s="3">
         <v>5600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5300</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,9 +2774,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,29 +2807,32 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2654,23 +2845,26 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1000</v>
+        <v>-3800</v>
       </c>
       <c r="E81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
+      <c r="G81" s="3">
+        <v>0</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2684,9 +2878,12 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,22 +2896,23 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
         <v>400</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+        <v>400</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2728,9 +2926,12 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,24 +3091,27 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-700</v>
+        <v>-5500</v>
       </c>
       <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
@@ -2908,9 +3124,12 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,23 +3142,24 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-900</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
@@ -2952,9 +3172,12 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,24 +3238,27 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4100</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3042,9 +3271,12 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,8 +3289,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3066,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3086,9 +3319,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,24 +3418,27 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>12300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5900</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3206,9 +3451,12 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3236,23 +3484,26 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E102" s="3">
         <v>11600</v>
-      </c>
-      <c r="E102" s="3">
-        <v>300</v>
       </c>
       <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+      <c r="G102" s="3">
+        <v>300</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -3266,7 +3517,10 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
   <si>
     <t>LASE</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -693,8 +693,8 @@
       <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
+      <c r="H7" s="2">
+        <v>43830</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
@@ -751,10 +751,10 @@
         <v>1500</v>
       </c>
       <c r="E9" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="F9" s="3">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="G9" s="3">
         <v>900</v>
@@ -787,7 +787,7 @@
         <v>1900</v>
       </c>
       <c r="F10" s="3">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="G10" s="3">
         <v>1200</v>
@@ -894,26 +894,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -939,14 +939,14 @@
       <c r="G15" s="3">
         <v>0</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -984,8 +984,8 @@
       <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
+      <c r="H17" s="3">
+        <v>100</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -1017,8 +1017,8 @@
       <c r="G18" s="3">
         <v>0</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+      <c r="H18" s="3">
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1056,14 +1056,14 @@
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1098,14 +1098,14 @@
       <c r="G21" s="3">
         <v>0</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1119,8 +1119,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1128,8 +1128,8 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1164,8 +1164,8 @@
       <c r="G23" s="3">
         <v>0</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
+      <c r="H23" s="3">
+        <v>0</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -1185,17 +1185,17 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1263,8 +1263,8 @@
       <c r="G26" s="3">
         <v>0</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
+      <c r="H26" s="3">
+        <v>0</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
@@ -1296,8 +1296,8 @@
       <c r="G27" s="3">
         <v>0</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
+      <c r="H27" s="3">
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1452,14 +1452,14 @@
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1494,8 +1494,8 @@
       <c r="G33" s="3">
         <v>0</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
+      <c r="H33" s="3">
+        <v>0</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
@@ -1560,8 +1560,8 @@
       <c r="G35" s="3">
         <v>0</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
+      <c r="H35" s="3">
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
@@ -1598,8 +1598,8 @@
       <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
+      <c r="H38" s="2">
+        <v>43830</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
@@ -1752,7 +1752,7 @@
         <v>2300</v>
       </c>
       <c r="E44" s="3">
-        <v>2700</v>
+        <v>1000</v>
       </c>
       <c r="F44" s="3">
         <v>1800</v>
@@ -1760,8 +1760,8 @@
       <c r="G44" s="3">
         <v>2200</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
+      <c r="H44" s="3">
+        <v>500</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
@@ -1826,8 +1826,8 @@
       <c r="G46" s="3">
         <v>3300</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
+      <c r="H46" s="3">
+        <v>500</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
@@ -1847,26 +1847,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1884,7 +1884,7 @@
         <v>1500</v>
       </c>
       <c r="E48" s="3">
-        <v>3400</v>
+        <v>1900</v>
       </c>
       <c r="F48" s="3">
         <v>1200</v>
@@ -1917,7 +1917,7 @@
         <v>4300</v>
       </c>
       <c r="E49" s="3">
-        <v>5900</v>
+        <v>2900</v>
       </c>
       <c r="F49" s="3">
         <v>3200</v>
@@ -1925,8 +1925,8 @@
       <c r="G49" s="3">
         <v>3200</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
+      <c r="H49" s="3">
+        <v>0</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
@@ -2015,14 +2015,14 @@
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>100</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2090,8 +2090,8 @@
       <c r="G54" s="3">
         <v>7500</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
+      <c r="H54" s="3">
+        <v>500</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
@@ -2147,14 +2147,14 @@
       <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
+      <c r="F57" s="3">
+        <v>100</v>
+      </c>
+      <c r="G57" s="3">
+        <v>100</v>
+      </c>
+      <c r="H57" s="3">
+        <v>0</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
@@ -2175,25 +2175,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2208,16 +2208,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="E59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
+        <v>100</v>
+      </c>
+      <c r="G59" s="3">
         <v>800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1000</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2252,8 +2252,8 @@
       <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
+      <c r="H60" s="3">
+        <v>0</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
@@ -2274,16 +2274,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2306,17 +2306,17 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>200</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3">
-        <v>500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>900</v>
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2450,8 +2450,8 @@
       <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
+      <c r="H66" s="3">
+        <v>0</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
@@ -2630,8 +2630,8 @@
       <c r="G72" s="3">
         <v>0</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
+      <c r="H72" s="3">
+        <v>0</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
@@ -2762,8 +2762,8 @@
       <c r="G76" s="3">
         <v>5300</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
+      <c r="H76" s="3">
+        <v>500</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
@@ -2833,8 +2833,8 @@
       <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
+      <c r="H80" s="2">
+        <v>43830</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
@@ -2866,8 +2866,8 @@
       <c r="G81" s="3">
         <v>0</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
+      <c r="H81" s="3">
+        <v>0</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
@@ -2903,10 +2903,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
@@ -3101,7 +3101,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-5500</v>
+        <v>-4300</v>
       </c>
       <c r="E89" s="3">
         <v>-100</v>
@@ -3112,8 +3112,8 @@
       <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="H89" s="3">
+        <v>-500</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
@@ -3296,13 +3296,13 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -3428,7 +3428,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="E100" s="3">
         <v>12300</v>
@@ -3439,8 +3439,8 @@
       <c r="G100" s="3">
         <v>5900</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="H100" s="3">
+        <v>3000</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -3460,26 +3460,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3505,14 +3505,14 @@
       <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="H102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>LASE</t>
   </si>
@@ -656,49 +656,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -708,27 +708,30 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="E8" s="3">
         <v>3900</v>
       </c>
       <c r="F8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G8" s="3">
         <v>4200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2200</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -741,27 +744,30 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="E9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="3">
         <v>2000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>900</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -774,27 +780,30 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F10" s="3">
         <v>1900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1200</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -807,9 +816,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,20 +835,21 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +868,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,14 +904,17 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -915,29 +934,32 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>400</v>
       </c>
       <c r="F15" s="3">
         <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -948,15 +970,18 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,29 +992,30 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7700</v>
+        <v>8900</v>
       </c>
       <c r="E17" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F17" s="3">
         <v>6000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>100</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,29 +1025,32 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3800</v>
+        <v>-5500</v>
       </c>
       <c r="E18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>600</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
         <v>0</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
+      <c r="I18" s="3">
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1032,9 +1061,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,22 +1080,23 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+        <v>-3900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1080,24 +1113,27 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3200</v>
+        <v>-600</v>
       </c>
       <c r="E21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1000</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
       <c r="H21" s="3">
         <v>0</v>
       </c>
@@ -1107,29 +1143,32 @@
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1146,29 +1185,32 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3800</v>
+        <v>-2500</v>
       </c>
       <c r="E23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>600</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
         <v>0</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
+      <c r="I23" s="3">
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1179,9 +1221,12 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1191,11 +1236,11 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1212,9 +1257,12 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,29 +1293,32 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3800</v>
+        <v>-2500</v>
       </c>
       <c r="E26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
         <v>0</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
+      <c r="I26" s="3">
+        <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1278,29 +1329,32 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3800</v>
+        <v>-9100</v>
       </c>
       <c r="E27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
         <v>0</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
+      <c r="I27" s="3">
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1311,9 +1365,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,23 +1509,26 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+        <v>3900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1476,29 +1545,32 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3800</v>
+        <v>-2500</v>
       </c>
       <c r="E33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
         <v>0</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
+      <c r="I33" s="3">
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1509,9 +1581,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,29 +1617,32 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3800</v>
+        <v>-2500</v>
       </c>
       <c r="E35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
         <v>0</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
+      <c r="I35" s="3">
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1575,35 +1653,38 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1613,9 +1694,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,26 +1729,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>6200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,9 +1762,12 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1709,27 +1798,30 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>800</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1742,9 +1834,12 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1752,20 +1847,20 @@
         <v>2300</v>
       </c>
       <c r="E44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F44" s="3">
         <v>1000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>500</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1775,21 +1870,24 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,33 +1903,36 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E46" s="3">
         <v>9300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>500</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1841,9 +1942,12 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1871,30 +1975,33 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1907,29 +2014,32 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E49" s="3">
         <v>4300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2900</v>
-      </c>
-      <c r="F49" s="3">
-        <v>3200</v>
       </c>
       <c r="G49" s="3">
         <v>3200</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+        <v>3200</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -1940,9 +2050,12 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,23 +2122,26 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>300</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2039,9 +2158,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,30 +2194,33 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>15200</v>
+        <v>17200</v>
       </c>
       <c r="E54" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F54" s="3">
         <v>18600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>500</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2105,9 +2230,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,28 +2265,29 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="E57" s="3">
         <v>200</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2165,63 +2295,69 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>200</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>200</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,29 +2370,32 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
       <c r="E60" s="3">
         <v>1000</v>
       </c>
       <c r="F60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G60" s="3">
         <v>400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
+      <c r="I60" s="3">
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2267,27 +2406,30 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1100</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2300,26 +2442,29 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2333,9 +2478,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,29 +2586,32 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1700</v>
+        <v>6900</v>
       </c>
       <c r="E66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F66" s="3">
         <v>1500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2200</v>
       </c>
-      <c r="H66" s="3">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
+      <c r="I66" s="3">
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2465,9 +2622,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,29 +2782,32 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-5700</v>
+        <v>-7800</v>
       </c>
       <c r="E72" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>300</v>
       </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
       <c r="H72" s="3">
         <v>0</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
+      <c r="I72" s="3">
+        <v>0</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2645,9 +2818,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,30 +2926,33 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>13500</v>
+        <v>10200</v>
       </c>
       <c r="E76" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F76" s="3">
         <v>17100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>500</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2962,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,35 +2998,38 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2848,29 +3039,32 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3800</v>
+        <v>-2500</v>
       </c>
       <c r="E81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
         <v>0</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
+      <c r="I81" s="3">
+        <v>0</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -2881,9 +3075,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,25 +3094,26 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>400</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -2929,9 +3127,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,30 +3307,33 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,9 +3343,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,26 +3362,27 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,9 +3395,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,27 +3467,30 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4100</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,9 +3503,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,23 +3522,24 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E96" s="3">
         <v>1200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>300</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,30 +3663,33 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3454,9 +3699,12 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3481,46 +3729,52 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11600</v>
-      </c>
-      <c r="F102" s="3">
-        <v>300</v>
       </c>
       <c r="G102" s="3">
         <v>300</v>
       </c>
       <c r="H102" s="3">
+        <v>300</v>
+      </c>
+      <c r="I102" s="3">
         <v>2500</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LASE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
   <si>
     <t>LASE</t>
   </si>
@@ -656,52 +656,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -711,30 +711,33 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3400</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3900</v>
       </c>
       <c r="F8" s="3">
         <v>3900</v>
       </c>
       <c r="G8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="H8" s="3">
         <v>4200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2200</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -747,30 +750,33 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1900</v>
+        <v>7100</v>
       </c>
       <c r="E9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>900</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -783,30 +789,33 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E10" s="3">
+        <v>400</v>
+      </c>
+      <c r="F10" s="3">
         <v>2900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1200</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -819,9 +828,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,23 +848,24 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E12" s="3">
+        <v>600</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,9 +884,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,17 +923,20 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>900</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+        <v>4100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-2900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -937,32 +956,35 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>400</v>
       </c>
       <c r="G15" s="3">
         <v>400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -973,15 +995,18 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,32 +1018,33 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E17" s="3">
         <v>8900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>100</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1028,32 +1054,35 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>600</v>
       </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
       <c r="I18" s="3">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+      <c r="J18" s="3">
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1064,9 +1093,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,25 +1113,26 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3900</v>
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1116,27 +1149,30 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-600</v>
+        <v>-7800</v>
       </c>
       <c r="E21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1000</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
         <v>0</v>
       </c>
@@ -1146,32 +1182,35 @@
       <c r="K21" s="3">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>4400</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1188,32 +1227,35 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>600</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+      <c r="J23" s="3">
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1224,9 +1266,12 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1239,11 +1284,11 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1260,9 +1305,12 @@
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,32 +1344,35 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+      <c r="J26" s="3">
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1332,32 +1383,35 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+      <c r="J27" s="3">
+        <v>0</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1368,9 +1422,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,26 +1578,29 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3900</v>
+        <v>200</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1548,32 +1617,35 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+      <c r="J33" s="3">
+        <v>0</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1584,9 +1656,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,32 +1695,35 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+      <c r="J35" s="3">
+        <v>0</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1656,38 +1734,41 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1697,9 +1778,12 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,29 +1815,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,9 +1851,12 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1801,30 +1890,33 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>800</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1837,33 +1929,36 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>500</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1873,24 +1968,27 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1906,36 +2004,39 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>500</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,9 +2046,12 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1978,33 +2082,36 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E48" s="3">
         <v>6700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,32 +2124,35 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>900</v>
+      </c>
+      <c r="E49" s="3">
         <v>5500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>3200</v>
       </c>
       <c r="H49" s="3">
         <v>3200</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>3200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2053,9 +2163,12 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,26 +2241,29 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>300</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="E52" s="3">
+        <v>300</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -2161,9 +2280,12 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,33 +2319,36 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E54" s="3">
         <v>17200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>500</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2233,9 +2358,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,31 +2395,32 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
-      </c>
-      <c r="E57" s="3">
-        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>200</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2298,69 +2428,75 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>200</v>
       </c>
       <c r="H58" s="3">
         <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,32 +2509,35 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2600</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1000</v>
       </c>
       <c r="F60" s="3">
         <v>1000</v>
       </c>
       <c r="G60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H60" s="3">
         <v>400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1000</v>
       </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="J60" s="3">
+        <v>0</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2409,30 +2548,33 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2445,9 +2587,12 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2457,17 +2602,17 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2481,9 +2626,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,32 +2743,35 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E66" s="3">
         <v>6900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2200</v>
       </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="J66" s="3">
+        <v>0</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2625,9 +2782,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,32 +2955,35 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-7800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>300</v>
       </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
       <c r="I72" s="3">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="J72" s="3">
+        <v>0</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2821,9 +2994,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,33 +3111,36 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>500</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,9 +3150,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,38 +3189,41 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3042,32 +3233,35 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+      <c r="J81" s="3">
+        <v>0</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3078,9 +3272,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,28 +3292,29 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>500</v>
+      </c>
+      <c r="E83" s="3">
         <v>600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>400</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3130,9 +3328,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,33 +3523,36 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3346,9 +3562,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,29 +3582,30 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3398,9 +3618,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,30 +3696,33 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4100</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,9 +3735,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,26 +3755,27 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E96" s="3">
         <v>5800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1200</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>300</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,33 +3908,36 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3702,9 +3947,12 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3732,49 +3980,55 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11600</v>
-      </c>
-      <c r="G102" s="3">
-        <v>300</v>
       </c>
       <c r="H102" s="3">
         <v>300</v>
       </c>
       <c r="I102" s="3">
+        <v>300</v>
+      </c>
+      <c r="J102" s="3">
         <v>2500</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
